--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2023.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,7 +701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Octubre 12-2023</t>
+          <t>Septiembre 25-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -715,72 +715,158 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6562.189</v>
+        <v>6562.101</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-9.5e-05</t>
+          <t>-0.00011</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-28.46</v>
+        <v>-32.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-51.51</v>
+        <v>-59.96</v>
       </c>
       <c r="H7" t="n">
-        <v>-50.7</v>
+        <v>-58.9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="J7" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Septiembre 29-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tierra</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6562.111</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-32.01</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-58.59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-58.01</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Octubre 12-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tierra</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6562.189</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-9.5e-05</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-28.46</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-51.51</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-50.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Octubre 19-2023</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Tierra</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Emisión Azul Hα</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>6562.118</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>-0.00011</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>-31.68</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
         <v>-52.29</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H10" t="n">
         <v>-54.13</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I10" t="n">
         <v>0.37</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>1.03</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K10" t="n">
         <v>0.52</v>
       </c>
     </row>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2023.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,7 +701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Septiembre 25-2023</t>
+          <t>Septiembre 21-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -715,36 +715,36 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6562.101</v>
+        <v>6562.167</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.00011</t>
+          <t>-9.8e-05</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-32.5</v>
+        <v>-29.47</v>
       </c>
       <c r="G7" t="n">
-        <v>-59.96</v>
+        <v>-57.65</v>
       </c>
       <c r="H7" t="n">
-        <v>-58.9</v>
+        <v>-58.88</v>
       </c>
       <c r="I7" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="J7" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="K7" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Septiembre 29-2023</t>
+          <t>Septiembre 25-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6562.111</v>
+        <v>6562.101</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-32.01</v>
+        <v>-32.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-58.59</v>
+        <v>-59.96</v>
       </c>
       <c r="H8" t="n">
-        <v>-58.01</v>
+        <v>-58.9</v>
       </c>
       <c r="I8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="J8" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="K8" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Octubre 12-2023</t>
+          <t>Septiembre 29-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -801,72 +801,115 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6562.189</v>
+        <v>6562.111</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-9.5e-05</t>
+          <t>-0.00011</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-28.46</v>
+        <v>-32.01</v>
       </c>
       <c r="G9" t="n">
-        <v>-51.51</v>
+        <v>-58.59</v>
       </c>
       <c r="H9" t="n">
-        <v>-50.7</v>
+        <v>-58.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="J9" t="n">
-        <v>1.08</v>
+        <v>0.97</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Octubre 12-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tierra</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6562.189</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-9.5e-05</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>-28.46</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-51.51</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-50.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Octubre 19-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Tierra</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Emisión Azul Hα</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>6562.118</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>-0.00011</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>-31.68</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>-52.29</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>-54.13</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>0.37</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1.03</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>0.52</v>
       </c>
     </row>
